--- a/ornek-veriler/ogrenci-aktarim-sablonu.xlsx
+++ b/ornek-veriler/ogrenci-aktarim-sablonu.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="125">
   <si>
-    <t>ogrenci-aktarim-sablonu (1)</t>
+    <t>ogrenci-aktarim-sablonu</t>
   </si>
   <si>
     <t>okul_no</t>
